--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_19-09-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_19-09-2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEA01C65-8161-4CC0-B463-35B388E0F4E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83AC6E01-B326-4E24-960E-E9A67E3E0E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1640,7 +1640,6 @@
   <dimension ref="A1:S29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="70.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
